--- a/docs/design/此刻校园_数据库表结构.xlsx
+++ b/docs/design/此刻校园_数据库表结构.xlsx
@@ -11,24 +11,20 @@
     <sheet name="schools" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="users" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="categories" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="post_types" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="tags" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="locations" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="posts" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="post_tags" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="post_images" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="comments" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="likes" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="favorites" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="validation_records" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="reports" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="notifications" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="topic_collections" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="topic_collection_posts" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="drafts" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="browse_histories" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="search_histories" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="admin_operation_logs" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="locations" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="posts" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="post_images" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="comments" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="likes" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="validation_records" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="reports" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="notifications" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="topic_collections" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="topic_collection_posts" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="drafts" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="browse_histories" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="search_histories" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="admin_operation_logs" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -563,7 +559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -584,7 +580,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>共 21 张表 | 数据库：openGauss 7.0.0-RC3 | 模拟核心：江南大学蠡湖校区</t>
+          <t>共 17 张表 | 数据库：openGauss 7.0.0-RC3 | 模拟核心：江南大学蠡湖校区</t>
         </is>
       </c>
     </row>
@@ -710,25 +706,25 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>post_types</t>
+          <t>locations</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>信息类型表</t>
+          <t>地点表</t>
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>信息类型，如活动、失物招领、寻物启事等</t>
+          <t>校园地点，含经纬度，关联学校</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>post_types</t>
+          <t>locations</t>
         </is>
       </c>
     </row>
@@ -738,25 +734,25 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>tags</t>
+          <t>posts</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>标签表</t>
+          <t>信息表</t>
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>信息标签，支持官方标签与用户自定义标签</t>
+          <t>核心表，存储校园信息，含6态状态机</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>tags</t>
+          <t>posts</t>
         </is>
       </c>
     </row>
@@ -766,25 +762,25 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>locations</t>
+          <t>post_images</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>地点表</t>
+          <t>信息图片表</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>校园地点，含经纬度，关联学校</t>
+          <t>信息的附图，一对多关联 Post</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>locations</t>
+          <t>post_images</t>
         </is>
       </c>
     </row>
@@ -794,25 +790,25 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>posts</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>信息表</t>
+          <t>评论表</t>
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>核心表，存储校园信息，含6态状态机</t>
+          <t>信息评论，支持自引用实现评论回复树</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>posts</t>
+          <t>comments</t>
         </is>
       </c>
     </row>
@@ -822,12 +818,12 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>post_tags</t>
+          <t>likes</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>信息标签关联表</t>
+          <t>点赞表</t>
         </is>
       </c>
       <c r="D12" s="4" t="n">
@@ -835,12 +831,12 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Post 与 Tag 的多对多关联表</t>
+          <t>用户对信息的点赞记录，post_id+user_id 联合唯一</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>post_tags</t>
+          <t>likes</t>
         </is>
       </c>
     </row>
@@ -850,25 +846,25 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>post_images</t>
+          <t>validation_records</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>信息图片表</t>
+          <t>协同验证记录表</t>
         </is>
       </c>
       <c r="D13" s="4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>信息的附图，一对多关联 Post</t>
+          <t>用户对信息的协同验证，仅含互斥的证实/证伪两类</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>post_images</t>
+          <t>validation_records</t>
         </is>
       </c>
     </row>
@@ -878,12 +874,12 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>reports</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>评论表</t>
+          <t>举报表</t>
         </is>
       </c>
       <c r="D14" s="4" t="n">
@@ -891,12 +887,12 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>信息评论，支持自引用实现评论回复树</t>
+          <t>用户举报信息或评论，含双角色引用（举报者+处理者）</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>reports</t>
         </is>
       </c>
     </row>
@@ -906,25 +902,25 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>likes</t>
+          <t>notifications</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>点赞表</t>
+          <t>通知表</t>
         </is>
       </c>
       <c r="D15" s="4" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>用户对信息的点赞记录，post_id+user_id 联合唯一</t>
+          <t>系统通知，含双角色引用（接收者+触发者），多态关联目标</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>likes</t>
+          <t>notifications</t>
         </is>
       </c>
     </row>
@@ -934,25 +930,25 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>favorites</t>
+          <t>topic_collections</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>收藏表</t>
+          <t>专题合集表</t>
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>用户对信息的收藏记录，post_id+user_id 联合唯一</t>
+          <t>专题合集，聚合多条相关信息</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>favorites</t>
+          <t>topic_collections</t>
         </is>
       </c>
     </row>
@@ -962,25 +958,25 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>validation_records</t>
+          <t>topic_collection_posts</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>协同验证记录表</t>
+          <t>专题信息关联表</t>
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>用户对信息的协同验证，含5类：证实/证伪/更新/过期报告/冲突报告</t>
+          <t>TopicCollection 与 Post 的多对多关联表</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>validation_records</t>
+          <t>topic_collection_posts</t>
         </is>
       </c>
     </row>
@@ -990,12 +986,12 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>reports</t>
+          <t>drafts</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>举报表</t>
+          <t>草稿表</t>
         </is>
       </c>
       <c r="D18" s="4" t="n">
@@ -1003,12 +999,12 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>用户举报信息或评论，含双角色引用（举报者+处理者）</t>
+          <t>用户信息草稿，自动保存未发布内容</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>reports</t>
+          <t>drafts</t>
         </is>
       </c>
     </row>
@@ -1018,25 +1014,25 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>notifications</t>
+          <t>browse_histories</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>通知表</t>
+          <t>浏览历史表</t>
         </is>
       </c>
       <c r="D19" s="4" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>系统通知，含双角色引用（接收者+触发者），多态关联目标</t>
+          <t>用户浏览信息的历史记录</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>notifications</t>
+          <t>browse_histories</t>
         </is>
       </c>
     </row>
@@ -1046,25 +1042,25 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>topic_collections</t>
+          <t>search_histories</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>专题合集表</t>
+          <t>搜索历史表</t>
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>专题合集，聚合多条相关信息</t>
+          <t>用户搜索关键词的历史记录</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>topic_collections</t>
+          <t>search_histories</t>
         </is>
       </c>
     </row>
@@ -1074,135 +1070,23 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>topic_collection_posts</t>
+          <t>admin_operation_logs</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>专题信息关联表</t>
+          <t>管理员操作日志表</t>
         </is>
       </c>
       <c r="D21" s="4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>TopicCollection 与 Post 的多对多关联表</t>
+          <t>管理员所有操作的审计日志</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>topic_collection_posts</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>drafts</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>草稿表</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>用户信息草稿，自动保存未发布内容</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>drafts</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>browse_histories</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>浏览历史表</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>用户浏览信息的历史记录</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>browse_histories</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>search_histories</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>搜索历史表</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>用户搜索关键词的历史记录</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>search_histories</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>admin_operation_logs</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>管理员操作日志表</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>管理员所有操作的审计日志</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
         <is>
           <t>admin_operation_logs</t>
         </is>
@@ -1223,7 +1107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1239,14 +1123,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>post_images（信息图片表）</t>
+          <t>validation_records（协同验证记录表）</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>说明：信息的附图，一对多关联 Post</t>
+          <t>说明：用户对信息的协同验证，仅含互斥的证实/证伪两类</t>
         </is>
       </c>
     </row>
@@ -1361,30 +1245,34 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n">
+      <c r="A7" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>image_url</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>VARCHAR(500)</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr"/>
-      <c r="E7" s="4" t="inlineStr"/>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr"/>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>图片URL</t>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>user_id</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr"/>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>→users</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="G7" s="13" t="inlineStr"/>
+      <c r="H7" s="13" t="inlineStr">
+        <is>
+          <t>验证者ID（外键）</t>
         </is>
       </c>
     </row>
@@ -1394,25 +1282,25 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>thumbnail_url</t>
+          <t>validation_type</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>VARCHAR(500)</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr"/>
       <c r="E8" s="4" t="inlineStr"/>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>NOT NULL</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr"/>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>缩略图URL</t>
+          <t>验证类型：confirmation/refutation</t>
         </is>
       </c>
     </row>
@@ -1422,29 +1310,25 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>sort_order</t>
+          <t>comment</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>VARCHAR(500)</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr"/>
       <c r="E9" s="4" t="inlineStr"/>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr"/>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>排序</t>
+          <t>验证评论</t>
         </is>
       </c>
     </row>
@@ -1454,173 +1338,29 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>file_size</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr"/>
       <c r="E10" s="4" t="inlineStr"/>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr"/>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>CURRENT</t>
+        </is>
+      </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>文件大小(字节)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>width</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>INTEGER</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr"/>
-      <c r="E11" s="4" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr"/>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>宽度(px)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>height</t>
-        </is>
-      </c>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>INTEGER</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr"/>
-      <c r="E12" s="4" t="inlineStr"/>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr"/>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>高度(px)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>created_at</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="inlineStr">
-        <is>
-          <t>TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr"/>
-      <c r="E13" s="4" t="inlineStr"/>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>CURRENT</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
           <t>创建时间</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>is_deleted</t>
-        </is>
-      </c>
-      <c r="C14" s="12" t="inlineStr">
-        <is>
-          <t>BOOLEAN</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr"/>
-      <c r="E14" s="4" t="inlineStr"/>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>软删除标记</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>deleted_at</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr"/>
-      <c r="E15" s="4" t="inlineStr"/>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr"/>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>删除时间</t>
         </is>
       </c>
     </row>
@@ -1655,14 +1395,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>comments（评论表）</t>
+          <t>reports（举报表）</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>说明：信息评论，支持自引用实现评论回复树</t>
+          <t>说明：用户举报信息或评论，含双角色引用（举报者+处理者）</t>
         </is>
       </c>
     </row>
@@ -1766,13 +1506,13 @@
       </c>
       <c r="F6" s="13" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="G6" s="13" t="inlineStr"/>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>信息ID（外键）</t>
+          <t>信息ID（外键，可空）</t>
         </is>
       </c>
     </row>
@@ -1782,7 +1522,7 @@
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>user_id</t>
+          <t>comment_id</t>
         </is>
       </c>
       <c r="C7" s="15" t="inlineStr">
@@ -1793,18 +1533,18 @@
       <c r="D7" s="13" t="inlineStr"/>
       <c r="E7" s="16" t="inlineStr">
         <is>
-          <t>→users</t>
+          <t>→comments</t>
         </is>
       </c>
       <c r="F7" s="13" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="G7" s="13" t="inlineStr"/>
       <c r="H7" s="13" t="inlineStr">
         <is>
-          <t>评论者ID（外键）</t>
+          <t>评论ID（外键，可空）</t>
         </is>
       </c>
     </row>
@@ -1814,7 +1554,7 @@
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>parent_id</t>
+          <t>reporter_id</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
@@ -1825,50 +1565,46 @@
       <c r="D8" s="13" t="inlineStr"/>
       <c r="E8" s="16" t="inlineStr">
         <is>
-          <t>→comments</t>
+          <t>→users</t>
         </is>
       </c>
       <c r="F8" s="13" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>NOT NULL</t>
         </is>
       </c>
       <c r="G8" s="13" t="inlineStr"/>
       <c r="H8" s="13" t="inlineStr">
         <is>
-          <t>父评论ID（自引用外键）</t>
+          <t>举报者ID（外键）</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="n">
+      <c r="A9" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>reply_to_user_id</t>
-        </is>
-      </c>
-      <c r="C9" s="15" t="inlineStr">
-        <is>
-          <t>BIGINT</t>
-        </is>
-      </c>
-      <c r="D9" s="13" t="inlineStr"/>
-      <c r="E9" s="16" t="inlineStr">
-        <is>
-          <t>→users</t>
-        </is>
-      </c>
-      <c r="F9" s="13" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="G9" s="13" t="inlineStr"/>
-      <c r="H9" s="13" t="inlineStr">
-        <is>
-          <t>回复目标用户ID（外键）</t>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>report_type</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>VARCHAR(30)</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr"/>
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>举报类型</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1614,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>content</t>
+          <t>description</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
@@ -1890,13 +1626,13 @@
       <c r="E10" s="4" t="inlineStr"/>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr"/>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>评论内容</t>
+          <t>举报描述</t>
         </is>
       </c>
     </row>
@@ -1906,12 +1642,12 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>like_count</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr"/>
@@ -1923,44 +1659,44 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>'pending'</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>点赞数</t>
+          <t>处理状态</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="n">
+      <c r="A12" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>VARCHAR(20)</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr"/>
-      <c r="E12" s="4" t="inlineStr"/>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>'pending'</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>状态</t>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>handler_id</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr"/>
+      <c r="E12" s="16" t="inlineStr">
+        <is>
+          <t>→users</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="G12" s="13" t="inlineStr"/>
+      <c r="H12" s="13" t="inlineStr">
+        <is>
+          <t>处理者ID（外键，可空）</t>
         </is>
       </c>
     </row>
@@ -1970,29 +1706,25 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>handle_result</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr"/>
       <c r="E13" s="4" t="inlineStr"/>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>CURRENT</t>
-        </is>
-      </c>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr"/>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>创建时间</t>
+          <t>处理结果</t>
         </is>
       </c>
     </row>
@@ -2002,7 +1734,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>handled_at</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
@@ -2014,17 +1746,13 @@
       <c r="E14" s="4" t="inlineStr"/>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>CURRENT</t>
-        </is>
-      </c>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr"/>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>更新时间</t>
+          <t>处理时间</t>
         </is>
       </c>
     </row>
@@ -2034,12 +1762,12 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>is_deleted</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>BOOLEAN</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr"/>
@@ -2051,12 +1779,12 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>CURRENT</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>软删除标记</t>
+          <t>创建时间</t>
         </is>
       </c>
     </row>
@@ -2066,7 +1794,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>deleted_at</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
@@ -2078,13 +1806,17 @@
       <c r="E16" s="4" t="inlineStr"/>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr"/>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>CURRENT</t>
+        </is>
+      </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>删除时间</t>
+          <t>更新时间</t>
         </is>
       </c>
     </row>
@@ -2103,7 +1835,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2119,14 +1851,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>likes（点赞表）</t>
+          <t>notifications（通知表）</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>说明：用户对信息的点赞记录，post_id+user_id 联合唯一</t>
+          <t>说明：系统通知，含双角色引用（接收者+触发者），多态关联目标</t>
         </is>
       </c>
     </row>
@@ -2214,7 +1946,7 @@
       </c>
       <c r="B6" s="14" t="inlineStr">
         <is>
-          <t>post_id</t>
+          <t>user_id</t>
         </is>
       </c>
       <c r="C6" s="15" t="inlineStr">
@@ -2225,7 +1957,7 @@
       <c r="D6" s="13" t="inlineStr"/>
       <c r="E6" s="16" t="inlineStr">
         <is>
-          <t>→posts</t>
+          <t>→users</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr">
@@ -2236,39 +1968,35 @@
       <c r="G6" s="13" t="inlineStr"/>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>信息ID（外键）</t>
+          <t>接收者ID（外键）</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="n">
+      <c r="A7" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="14" t="inlineStr">
-        <is>
-          <t>user_id</t>
-        </is>
-      </c>
-      <c r="C7" s="15" t="inlineStr">
-        <is>
-          <t>BIGINT</t>
-        </is>
-      </c>
-      <c r="D7" s="13" t="inlineStr"/>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>→users</t>
-        </is>
-      </c>
-      <c r="F7" s="13" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G7" s="13" t="inlineStr"/>
-      <c r="H7" s="13" t="inlineStr">
-        <is>
-          <t>用户ID（外键）</t>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>VARCHAR(30)</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr"/>
+      <c r="E7" s="4" t="inlineStr"/>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>通知类型</t>
         </is>
       </c>
     </row>
@@ -2278,12 +2006,12 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>title</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>VARCHAR(200)</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr"/>
@@ -2293,14 +2021,278 @@
           <t>NOT NULL</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>通知标题</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>content</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>VARCHAR(500)</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr"/>
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>通知内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>target_type</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>VARCHAR(50)</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr"/>
+      <c r="E10" s="4" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>目标类型（多态）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>target_id</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr"/>
+      <c r="E11" s="4" t="inlineStr"/>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>目标ID（多态）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>actor_id</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr"/>
+      <c r="E12" s="16" t="inlineStr">
+        <is>
+          <t>→users</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="G12" s="13" t="inlineStr"/>
+      <c r="H12" s="13" t="inlineStr">
+        <is>
+          <t>触发者ID（外键，可空）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>is_read</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>BOOLEAN</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr"/>
+      <c r="E13" s="4" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>是否已读</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>read_at</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr"/>
+      <c r="E14" s="4" t="inlineStr"/>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr"/>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>阅读时间</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr"/>
+      <c r="E15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>CURRENT</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
         <is>
           <t>创建时间</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>is_deleted</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>BOOLEAN</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr"/>
+      <c r="E16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>软删除标记</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>deleted_at</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr"/>
+      <c r="E17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr"/>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>删除时间</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2311,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2335,14 +2327,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>favorites（收藏表）</t>
+          <t>topic_collections（专题合集表）</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>说明：用户对信息的收藏记录，post_id+user_id 联合唯一</t>
+          <t>说明：专题合集，聚合多条相关信息</t>
         </is>
       </c>
     </row>
@@ -2425,66 +2417,58 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="n">
+      <c r="A6" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="14" t="inlineStr">
-        <is>
-          <t>post_id</t>
-        </is>
-      </c>
-      <c r="C6" s="15" t="inlineStr">
-        <is>
-          <t>BIGINT</t>
-        </is>
-      </c>
-      <c r="D6" s="13" t="inlineStr"/>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>→posts</t>
-        </is>
-      </c>
-      <c r="F6" s="13" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G6" s="13" t="inlineStr"/>
-      <c r="H6" s="13" t="inlineStr">
-        <is>
-          <t>信息ID（外键）</t>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>VARCHAR(200)</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr"/>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>专题标题</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="n">
+      <c r="A7" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="14" t="inlineStr">
-        <is>
-          <t>user_id</t>
-        </is>
-      </c>
-      <c r="C7" s="15" t="inlineStr">
-        <is>
-          <t>BIGINT</t>
-        </is>
-      </c>
-      <c r="D7" s="13" t="inlineStr"/>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>→users</t>
-        </is>
-      </c>
-      <c r="F7" s="13" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G7" s="13" t="inlineStr"/>
-      <c r="H7" s="13" t="inlineStr">
-        <is>
-          <t>用户ID（外键）</t>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr"/>
+      <c r="E7" s="4" t="inlineStr"/>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>专题描述</t>
         </is>
       </c>
     </row>
@@ -2494,29 +2478,369 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>cover_url</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>VARCHAR(500)</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr"/>
       <c r="E8" s="4" t="inlineStr"/>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>封面URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>school_id</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr"/>
+      <c r="E9" s="16" t="inlineStr">
+        <is>
+          <t>→schools</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="G9" s="13" t="inlineStr"/>
+      <c r="H9" s="13" t="inlineStr">
+        <is>
+          <t>学校ID（外键）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>creator_id</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr"/>
+      <c r="E10" s="16" t="inlineStr">
+        <is>
+          <t>→users</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="G10" s="13" t="inlineStr"/>
+      <c r="H10" s="13" t="inlineStr">
+        <is>
+          <t>创建者ID（外键）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>post_count</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr"/>
+      <c r="E11" s="4" t="inlineStr"/>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>信息数</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>view_count</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr"/>
+      <c r="E12" s="4" t="inlineStr"/>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>浏览数</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>VARCHAR(20)</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr"/>
+      <c r="E13" s="4" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>'draft'</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>sort_order</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr"/>
+      <c r="E14" s="4" t="inlineStr"/>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>排序</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>published_at</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr"/>
+      <c r="E15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr"/>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>发布时间</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr"/>
+      <c r="E16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>CURRENT</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H16" s="4" t="inlineStr">
         <is>
           <t>创建时间</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr"/>
+      <c r="E17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>CURRENT</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>更新时间</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>is_deleted</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>BOOLEAN</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr"/>
+      <c r="E18" s="4" t="inlineStr"/>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>软删除标记</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>deleted_at</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr"/>
+      <c r="E19" s="4" t="inlineStr"/>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr"/>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>删除时间</t>
         </is>
       </c>
     </row>
@@ -2535,7 +2859,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2551,14 +2875,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>validation_records（协同验证记录表）</t>
+          <t>topic_collection_posts（专题信息关联表）</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>说明：用户对信息的协同验证，含5类：证实/证伪/更新/过期报告/冲突报告</t>
+          <t>说明：TopicCollection 与 Post 的多对多关联表</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2970,7 @@
       </c>
       <c r="B6" s="14" t="inlineStr">
         <is>
-          <t>post_id</t>
+          <t>topic_collection_id</t>
         </is>
       </c>
       <c r="C6" s="15" t="inlineStr">
@@ -2657,7 +2981,7 @@
       <c r="D6" s="13" t="inlineStr"/>
       <c r="E6" s="16" t="inlineStr">
         <is>
-          <t>→posts</t>
+          <t>→topic_collections</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr">
@@ -2668,7 +2992,7 @@
       <c r="G6" s="13" t="inlineStr"/>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>信息ID（外键）</t>
+          <t>专题ID（外键）</t>
         </is>
       </c>
     </row>
@@ -2678,7 +3002,7 @@
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>user_id</t>
+          <t>post_id</t>
         </is>
       </c>
       <c r="C7" s="15" t="inlineStr">
@@ -2689,7 +3013,7 @@
       <c r="D7" s="13" t="inlineStr"/>
       <c r="E7" s="16" t="inlineStr">
         <is>
-          <t>→users</t>
+          <t>→posts</t>
         </is>
       </c>
       <c r="F7" s="13" t="inlineStr">
@@ -2700,7 +3024,7 @@
       <c r="G7" s="13" t="inlineStr"/>
       <c r="H7" s="13" t="inlineStr">
         <is>
-          <t>验证者ID（外键）</t>
+          <t>信息ID（外键）</t>
         </is>
       </c>
     </row>
@@ -2710,12 +3034,12 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>validation_type</t>
+          <t>sort_order</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>VARCHAR(30)</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr"/>
@@ -2725,10 +3049,14 @@
           <t>NOT NULL</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr"/>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>验证类型：5类</t>
+          <t>排序</t>
         </is>
       </c>
     </row>
@@ -2738,55 +3066,27 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>comment</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>VARCHAR(500)</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr"/>
       <c r="E9" s="4" t="inlineStr"/>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr"/>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>CURRENT</t>
+        </is>
+      </c>
       <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>验证评论</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>created_at</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr"/>
-      <c r="E10" s="4" t="inlineStr"/>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>CURRENT</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>创建时间</t>
         </is>
@@ -2823,14 +3123,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>reports（举报表）</t>
+          <t>drafts（草稿表）</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>说明：用户举报信息或评论，含双角色引用（举报者+处理者）</t>
+          <t>说明：用户信息草稿，自动保存未发布内容</t>
         </is>
       </c>
     </row>
@@ -2918,7 +3218,7 @@
       </c>
       <c r="B6" s="14" t="inlineStr">
         <is>
-          <t>post_id</t>
+          <t>user_id</t>
         </is>
       </c>
       <c r="C6" s="15" t="inlineStr">
@@ -2929,138 +3229,138 @@
       <c r="D6" s="13" t="inlineStr"/>
       <c r="E6" s="16" t="inlineStr">
         <is>
-          <t>→posts</t>
+          <t>→users</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>NOT NULL</t>
         </is>
       </c>
       <c r="G6" s="13" t="inlineStr"/>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>信息ID（外键，可空）</t>
+          <t>用户ID（外键）</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="n">
+      <c r="A7" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="14" t="inlineStr">
-        <is>
-          <t>comment_id</t>
-        </is>
-      </c>
-      <c r="C7" s="15" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>VARCHAR(200)</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr"/>
+      <c r="E7" s="4" t="inlineStr"/>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>草稿标题</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>content</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr"/>
+      <c r="E8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>草稿内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>category_id</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>BIGINT</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr"/>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>→comments</t>
-        </is>
-      </c>
-      <c r="F7" s="13" t="inlineStr">
+      <c r="D9" s="13" t="inlineStr"/>
+      <c r="E9" s="16" t="inlineStr">
+        <is>
+          <t>→categories</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="G7" s="13" t="inlineStr"/>
-      <c r="H7" s="13" t="inlineStr">
-        <is>
-          <t>评论ID（外键，可空）</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="14" t="inlineStr">
-        <is>
-          <t>reporter_id</t>
-        </is>
-      </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="G9" s="13" t="inlineStr"/>
+      <c r="H9" s="13" t="inlineStr">
+        <is>
+          <t>分类ID（外键，可空）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>location_id</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
         <is>
           <t>BIGINT</t>
         </is>
       </c>
-      <c r="D8" s="13" t="inlineStr"/>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>→users</t>
-        </is>
-      </c>
-      <c r="F8" s="13" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G8" s="13" t="inlineStr"/>
-      <c r="H8" s="13" t="inlineStr">
-        <is>
-          <t>举报者ID（外键）</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>report_type</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>VARCHAR(30)</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr"/>
-      <c r="E9" s="4" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr"/>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>举报类型</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr"/>
-      <c r="E10" s="4" t="inlineStr"/>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="D10" s="13" t="inlineStr"/>
+      <c r="E10" s="16" t="inlineStr">
+        <is>
+          <t>→locations</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr"/>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>举报描述</t>
+      <c r="G10" s="13" t="inlineStr"/>
+      <c r="H10" s="13" t="inlineStr">
+        <is>
+          <t>地点ID（外键，可空）</t>
         </is>
       </c>
     </row>
@@ -3070,12 +3370,12 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>is_anonymous</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
+          <t>BOOLEAN</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr"/>
@@ -3087,44 +3387,40 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>'pending'</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>处理状态</t>
+          <t>是否匿名</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="n">
+      <c r="A12" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>handler_id</t>
-        </is>
-      </c>
-      <c r="C12" s="15" t="inlineStr">
-        <is>
-          <t>BIGINT</t>
-        </is>
-      </c>
-      <c r="D12" s="13" t="inlineStr"/>
-      <c r="E12" s="16" t="inlineStr">
-        <is>
-          <t>→users</t>
-        </is>
-      </c>
-      <c r="F12" s="13" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>extra_data</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr"/>
+      <c r="E12" s="4" t="inlineStr"/>
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="G12" s="13" t="inlineStr"/>
-      <c r="H12" s="13" t="inlineStr">
-        <is>
-          <t>处理者ID（外键，可空）</t>
+      <c r="G12" s="4" t="inlineStr"/>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>额外数据(JSON)</t>
         </is>
       </c>
     </row>
@@ -3134,25 +3430,29 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>handle_result</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr"/>
       <c r="E13" s="4" t="inlineStr"/>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr"/>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>CURRENT</t>
+        </is>
+      </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>处理结果</t>
+          <t>创建时间</t>
         </is>
       </c>
     </row>
@@ -3162,7 +3462,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>handled_at</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
@@ -3174,13 +3474,17 @@
       <c r="E14" s="4" t="inlineStr"/>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr"/>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>CURRENT</t>
+        </is>
+      </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>处理时间</t>
+          <t>更新时间</t>
         </is>
       </c>
     </row>
@@ -3190,12 +3494,12 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>is_deleted</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>BOOLEAN</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr"/>
@@ -3207,12 +3511,12 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>CURRENT</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>创建时间</t>
+          <t>软删除标记</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3526,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>deleted_at</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
@@ -3234,17 +3538,13 @@
       <c r="E16" s="4" t="inlineStr"/>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>CURRENT</t>
-        </is>
-      </c>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr"/>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>更新时间</t>
+          <t>删除时间</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3279,14 +3579,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>notifications（通知表）</t>
+          <t>browse_histories（浏览历史表）</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>说明：系统通知，含双角色引用（接收者+触发者），多态关联目标</t>
+          <t>说明：用户浏览信息的历史记录</t>
         </is>
       </c>
     </row>
@@ -3396,35 +3696,39 @@
       <c r="G6" s="13" t="inlineStr"/>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>接收者ID（外键）</t>
+          <t>用户ID（外键）</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n">
+      <c r="A7" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>VARCHAR(30)</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr"/>
-      <c r="E7" s="4" t="inlineStr"/>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr"/>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>通知类型</t>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>post_id</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr"/>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>→posts</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="G7" s="13" t="inlineStr"/>
+      <c r="H7" s="13" t="inlineStr">
+        <is>
+          <t>信息ID（外键）</t>
         </is>
       </c>
     </row>
@@ -3434,12 +3738,12 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>VARCHAR(200)</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr"/>
@@ -3449,278 +3753,14 @@
           <t>NOT NULL</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr"/>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>CURRENT</t>
+        </is>
+      </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>通知标题</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>content</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>VARCHAR(500)</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr"/>
-      <c r="E9" s="4" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr"/>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>通知内容</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>target_type</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>VARCHAR(50)</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr"/>
-      <c r="E10" s="4" t="inlineStr"/>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr"/>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>目标类型（多态）</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>target_id</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>BIGINT</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr"/>
-      <c r="E11" s="4" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr"/>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>目标ID（多态）</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>actor_id</t>
-        </is>
-      </c>
-      <c r="C12" s="15" t="inlineStr">
-        <is>
-          <t>BIGINT</t>
-        </is>
-      </c>
-      <c r="D12" s="13" t="inlineStr"/>
-      <c r="E12" s="16" t="inlineStr">
-        <is>
-          <t>→users</t>
-        </is>
-      </c>
-      <c r="F12" s="13" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="G12" s="13" t="inlineStr"/>
-      <c r="H12" s="13" t="inlineStr">
-        <is>
-          <t>触发者ID（外键，可空）</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>is_read</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="inlineStr">
-        <is>
-          <t>BOOLEAN</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr"/>
-      <c r="E13" s="4" t="inlineStr"/>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>是否已读</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>read_at</t>
-        </is>
-      </c>
-      <c r="C14" s="12" t="inlineStr">
-        <is>
-          <t>TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr"/>
-      <c r="E14" s="4" t="inlineStr"/>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr"/>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>阅读时间</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>created_at</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr"/>
-      <c r="E15" s="4" t="inlineStr"/>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>CURRENT</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>创建时间</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>is_deleted</t>
-        </is>
-      </c>
-      <c r="C16" s="12" t="inlineStr">
-        <is>
-          <t>BOOLEAN</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr"/>
-      <c r="E16" s="4" t="inlineStr"/>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>软删除标记</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>deleted_at</t>
-        </is>
-      </c>
-      <c r="C17" s="12" t="inlineStr">
-        <is>
-          <t>TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr"/>
-      <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr"/>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>删除时间</t>
+          <t>浏览时间</t>
         </is>
       </c>
     </row>
@@ -3734,554 +3774,6 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>topic_collections（专题合集表）</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>说明：专题合集，聚合多条相关信息</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="25" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>序号</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>字段名</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>数据类型</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>主键</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>外键</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>可空</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>默认值</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>说明</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="inlineStr">
-        <is>
-          <t>BIGINT</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr"/>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
-          <t>AUTO</t>
-        </is>
-      </c>
-      <c r="H5" s="8" t="inlineStr">
-        <is>
-          <t>主键，自增</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>VARCHAR(200)</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr"/>
-      <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>专题标题</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr"/>
-      <c r="E7" s="4" t="inlineStr"/>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr"/>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>专题描述</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>cover_url</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>VARCHAR(500)</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr"/>
-      <c r="E8" s="4" t="inlineStr"/>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr"/>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>封面URL</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>school_id</t>
-        </is>
-      </c>
-      <c r="C9" s="15" t="inlineStr">
-        <is>
-          <t>BIGINT</t>
-        </is>
-      </c>
-      <c r="D9" s="13" t="inlineStr"/>
-      <c r="E9" s="16" t="inlineStr">
-        <is>
-          <t>→schools</t>
-        </is>
-      </c>
-      <c r="F9" s="13" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G9" s="13" t="inlineStr"/>
-      <c r="H9" s="13" t="inlineStr">
-        <is>
-          <t>学校ID（外键）</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>creator_id</t>
-        </is>
-      </c>
-      <c r="C10" s="15" t="inlineStr">
-        <is>
-          <t>BIGINT</t>
-        </is>
-      </c>
-      <c r="D10" s="13" t="inlineStr"/>
-      <c r="E10" s="16" t="inlineStr">
-        <is>
-          <t>→users</t>
-        </is>
-      </c>
-      <c r="F10" s="13" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G10" s="13" t="inlineStr"/>
-      <c r="H10" s="13" t="inlineStr">
-        <is>
-          <t>创建者ID（外键）</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>post_count</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>INTEGER</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr"/>
-      <c r="E11" s="4" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>信息数</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>view_count</t>
-        </is>
-      </c>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>INTEGER</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr"/>
-      <c r="E12" s="4" t="inlineStr"/>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>浏览数</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="inlineStr">
-        <is>
-          <t>VARCHAR(20)</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr"/>
-      <c r="E13" s="4" t="inlineStr"/>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>'draft'</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>sort_order</t>
-        </is>
-      </c>
-      <c r="C14" s="12" t="inlineStr">
-        <is>
-          <t>INTEGER</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr"/>
-      <c r="E14" s="4" t="inlineStr"/>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>排序</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>published_at</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr"/>
-      <c r="E15" s="4" t="inlineStr"/>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr"/>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>发布时间</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>created_at</t>
-        </is>
-      </c>
-      <c r="C16" s="12" t="inlineStr">
-        <is>
-          <t>TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr"/>
-      <c r="E16" s="4" t="inlineStr"/>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>CURRENT</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>创建时间</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>updated_at</t>
-        </is>
-      </c>
-      <c r="C17" s="12" t="inlineStr">
-        <is>
-          <t>TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr"/>
-      <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>CURRENT</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>更新时间</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>is_deleted</t>
-        </is>
-      </c>
-      <c r="C18" s="12" t="inlineStr">
-        <is>
-          <t>BOOLEAN</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr"/>
-      <c r="E18" s="4" t="inlineStr"/>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>软删除标记</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>deleted_at</t>
-        </is>
-      </c>
-      <c r="C19" s="12" t="inlineStr">
-        <is>
-          <t>TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr"/>
-      <c r="E19" s="4" t="inlineStr"/>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr"/>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>删除时间</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4303,14 +3795,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>topic_collection_posts（专题信息关联表）</t>
+          <t>search_histories（搜索历史表）</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>说明：TopicCollection 与 Post 的多对多关联表</t>
+          <t>说明：用户搜索关键词的历史记录</t>
         </is>
       </c>
     </row>
@@ -4398,7 +3890,7 @@
       </c>
       <c r="B6" s="14" t="inlineStr">
         <is>
-          <t>topic_collection_id</t>
+          <t>user_id</t>
         </is>
       </c>
       <c r="C6" s="15" t="inlineStr">
@@ -4409,7 +3901,7 @@
       <c r="D6" s="13" t="inlineStr"/>
       <c r="E6" s="16" t="inlineStr">
         <is>
-          <t>→topic_collections</t>
+          <t>→users</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr">
@@ -4420,39 +3912,35 @@
       <c r="G6" s="13" t="inlineStr"/>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>专题ID（外键）</t>
+          <t>用户ID（外键）</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="n">
+      <c r="A7" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="14" t="inlineStr">
-        <is>
-          <t>post_id</t>
-        </is>
-      </c>
-      <c r="C7" s="15" t="inlineStr">
-        <is>
-          <t>BIGINT</t>
-        </is>
-      </c>
-      <c r="D7" s="13" t="inlineStr"/>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>→posts</t>
-        </is>
-      </c>
-      <c r="F7" s="13" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G7" s="13" t="inlineStr"/>
-      <c r="H7" s="13" t="inlineStr">
-        <is>
-          <t>信息ID（外键）</t>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>VARCHAR(200)</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr"/>
+      <c r="E7" s="4" t="inlineStr"/>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>搜索关键词</t>
         </is>
       </c>
     </row>
@@ -4462,7 +3950,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>sort_order</t>
+          <t>result_count</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -4474,17 +3962,13 @@
       <c r="E8" s="4" t="inlineStr"/>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr"/>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>排序</t>
+          <t>结果数量</t>
         </is>
       </c>
     </row>
@@ -4516,7 +4000,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>创建时间</t>
+          <t>搜索时间</t>
         </is>
       </c>
     </row>
@@ -4529,13 +4013,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4551,14 +4035,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>drafts（草稿表）</t>
+          <t>admin_operation_logs（管理员操作日志表）</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>说明：用户信息草稿，自动保存未发布内容</t>
+          <t>说明：管理员所有操作的审计日志</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4130,7 @@
       </c>
       <c r="B6" s="14" t="inlineStr">
         <is>
-          <t>user_id</t>
+          <t>admin_id</t>
         </is>
       </c>
       <c r="C6" s="15" t="inlineStr">
@@ -4668,7 +4152,7 @@
       <c r="G6" s="13" t="inlineStr"/>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>用户ID（外键）</t>
+          <t>管理员ID（外键）</t>
         </is>
       </c>
     </row>
@@ -4678,25 +4162,25 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>action</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>VARCHAR(200)</t>
+          <t>VARCHAR(50)</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr"/>
       <c r="E7" s="4" t="inlineStr"/>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>NOT NULL</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr"/>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>草稿标题</t>
+          <t>操作类型</t>
         </is>
       </c>
     </row>
@@ -4706,121 +4190,109 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>content</t>
+          <t>target_type</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>VARCHAR(50)</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr"/>
       <c r="E8" s="4" t="inlineStr"/>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>NOT NULL</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr"/>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>草稿内容</t>
+          <t>目标类型</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="n">
+      <c r="A9" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>category_id</t>
-        </is>
-      </c>
-      <c r="C9" s="15" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>target_id</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>BIGINT</t>
         </is>
       </c>
-      <c r="D9" s="13" t="inlineStr"/>
-      <c r="E9" s="16" t="inlineStr">
-        <is>
-          <t>→categories</t>
-        </is>
-      </c>
-      <c r="F9" s="13" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr"/>
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>目标ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>detail</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr"/>
+      <c r="E10" s="4" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="G9" s="13" t="inlineStr"/>
-      <c r="H9" s="13" t="inlineStr">
-        <is>
-          <t>分类ID（外键，可空）</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>post_type_id</t>
-        </is>
-      </c>
-      <c r="C10" s="15" t="inlineStr">
-        <is>
-          <t>BIGINT</t>
-        </is>
-      </c>
-      <c r="D10" s="13" t="inlineStr"/>
-      <c r="E10" s="16" t="inlineStr">
-        <is>
-          <t>→post_types</t>
-        </is>
-      </c>
-      <c r="F10" s="13" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>操作详情</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>ip_address</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>VARCHAR(45)</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr"/>
+      <c r="E11" s="4" t="inlineStr"/>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="G10" s="13" t="inlineStr"/>
-      <c r="H10" s="13" t="inlineStr">
-        <is>
-          <t>类型ID（外键，可空）</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="13" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>location_id</t>
-        </is>
-      </c>
-      <c r="C11" s="15" t="inlineStr">
-        <is>
-          <t>BIGINT</t>
-        </is>
-      </c>
-      <c r="D11" s="13" t="inlineStr"/>
-      <c r="E11" s="16" t="inlineStr">
-        <is>
-          <t>→locations</t>
-        </is>
-      </c>
-      <c r="F11" s="13" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="G11" s="13" t="inlineStr"/>
-      <c r="H11" s="13" t="inlineStr">
-        <is>
-          <t>地点ID（外键，可空）</t>
+      <c r="G11" s="4" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>IP地址</t>
         </is>
       </c>
     </row>
@@ -4830,29 +4302,25 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>is_anonymous</t>
+          <t>user_agent</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>BOOLEAN</t>
+          <t>VARCHAR(500)</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr"/>
       <c r="E12" s="4" t="inlineStr"/>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr"/>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>是否匿名</t>
+          <t>User-Agent</t>
         </is>
       </c>
     </row>
@@ -4862,149 +4330,29 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>extra_data</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr"/>
       <c r="E13" s="4" t="inlineStr"/>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr"/>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>CURRENT</t>
+        </is>
+      </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>额外数据(JSON)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>created_at</t>
-        </is>
-      </c>
-      <c r="C14" s="12" t="inlineStr">
-        <is>
-          <t>TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr"/>
-      <c r="E14" s="4" t="inlineStr"/>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>CURRENT</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>创建时间</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>updated_at</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr"/>
-      <c r="E15" s="4" t="inlineStr"/>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>CURRENT</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>更新时间</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>is_deleted</t>
-        </is>
-      </c>
-      <c r="C16" s="12" t="inlineStr">
-        <is>
-          <t>BOOLEAN</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr"/>
-      <c r="E16" s="4" t="inlineStr"/>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>软删除标记</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>deleted_at</t>
-        </is>
-      </c>
-      <c r="C17" s="12" t="inlineStr">
-        <is>
-          <t>TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr"/>
-      <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr"/>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>删除时间</t>
+          <t>操作时间</t>
         </is>
       </c>
     </row>
@@ -5489,814 +4837,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>browse_histories（浏览历史表）</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>说明：用户浏览信息的历史记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="25" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>序号</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>字段名</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>数据类型</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>主键</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>外键</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>可空</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>默认值</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>说明</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="inlineStr">
-        <is>
-          <t>BIGINT</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr"/>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
-          <t>AUTO</t>
-        </is>
-      </c>
-      <c r="H5" s="8" t="inlineStr">
-        <is>
-          <t>主键，自增</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="14" t="inlineStr">
-        <is>
-          <t>user_id</t>
-        </is>
-      </c>
-      <c r="C6" s="15" t="inlineStr">
-        <is>
-          <t>BIGINT</t>
-        </is>
-      </c>
-      <c r="D6" s="13" t="inlineStr"/>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>→users</t>
-        </is>
-      </c>
-      <c r="F6" s="13" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G6" s="13" t="inlineStr"/>
-      <c r="H6" s="13" t="inlineStr">
-        <is>
-          <t>用户ID（外键）</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="14" t="inlineStr">
-        <is>
-          <t>post_id</t>
-        </is>
-      </c>
-      <c r="C7" s="15" t="inlineStr">
-        <is>
-          <t>BIGINT</t>
-        </is>
-      </c>
-      <c r="D7" s="13" t="inlineStr"/>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>→posts</t>
-        </is>
-      </c>
-      <c r="F7" s="13" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G7" s="13" t="inlineStr"/>
-      <c r="H7" s="13" t="inlineStr">
-        <is>
-          <t>信息ID（外键）</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>created_at</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr"/>
-      <c r="E8" s="4" t="inlineStr"/>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>CURRENT</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>浏览时间</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>search_histories（搜索历史表）</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>说明：用户搜索关键词的历史记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="25" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>序号</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>字段名</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>数据类型</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>主键</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>外键</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>可空</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>默认值</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>说明</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="inlineStr">
-        <is>
-          <t>BIGINT</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr"/>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
-          <t>AUTO</t>
-        </is>
-      </c>
-      <c r="H5" s="8" t="inlineStr">
-        <is>
-          <t>主键，自增</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="14" t="inlineStr">
-        <is>
-          <t>user_id</t>
-        </is>
-      </c>
-      <c r="C6" s="15" t="inlineStr">
-        <is>
-          <t>BIGINT</t>
-        </is>
-      </c>
-      <c r="D6" s="13" t="inlineStr"/>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>→users</t>
-        </is>
-      </c>
-      <c r="F6" s="13" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G6" s="13" t="inlineStr"/>
-      <c r="H6" s="13" t="inlineStr">
-        <is>
-          <t>用户ID（外键）</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>keyword</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>VARCHAR(200)</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr"/>
-      <c r="E7" s="4" t="inlineStr"/>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr"/>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>搜索关键词</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>result_count</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>INTEGER</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr"/>
-      <c r="E8" s="4" t="inlineStr"/>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr"/>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>结果数量</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>created_at</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr"/>
-      <c r="E9" s="4" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>CURRENT</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>搜索时间</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>admin_operation_logs（管理员操作日志表）</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>说明：管理员所有操作的审计日志</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="25" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>序号</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>字段名</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>数据类型</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>主键</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>外键</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>可空</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>默认值</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>说明</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="inlineStr">
-        <is>
-          <t>BIGINT</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr"/>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
-          <t>AUTO</t>
-        </is>
-      </c>
-      <c r="H5" s="8" t="inlineStr">
-        <is>
-          <t>主键，自增</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="14" t="inlineStr">
-        <is>
-          <t>admin_id</t>
-        </is>
-      </c>
-      <c r="C6" s="15" t="inlineStr">
-        <is>
-          <t>BIGINT</t>
-        </is>
-      </c>
-      <c r="D6" s="13" t="inlineStr"/>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>→users</t>
-        </is>
-      </c>
-      <c r="F6" s="13" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G6" s="13" t="inlineStr"/>
-      <c r="H6" s="13" t="inlineStr">
-        <is>
-          <t>管理员ID（外键）</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>action</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>VARCHAR(50)</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr"/>
-      <c r="E7" s="4" t="inlineStr"/>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr"/>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>操作类型</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>target_type</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>VARCHAR(50)</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr"/>
-      <c r="E8" s="4" t="inlineStr"/>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr"/>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>目标类型</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>target_id</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>BIGINT</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr"/>
-      <c r="E9" s="4" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr"/>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>目标ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>detail</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr"/>
-      <c r="E10" s="4" t="inlineStr"/>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr"/>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>操作详情</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>ip_address</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>VARCHAR(45)</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr"/>
-      <c r="E11" s="4" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr"/>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>IP地址</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>user_agent</t>
-        </is>
-      </c>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>VARCHAR(500)</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr"/>
-      <c r="E12" s="4" t="inlineStr"/>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr"/>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>User-Agent</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>created_at</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="inlineStr">
-        <is>
-          <t>TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr"/>
-      <c r="E13" s="4" t="inlineStr"/>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>CURRENT</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>操作时间</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -7203,7 +5743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7219,14 +5759,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>post_types（信息类型表）</t>
+          <t>locations（地点表）</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>说明：信息类型，如活动、失物招领、寻物启事等</t>
+          <t>说明：校园地点，含经纬度，关联学校</t>
         </is>
       </c>
     </row>
@@ -7309,30 +5849,34 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="n">
+      <c r="A6" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>VARCHAR(50)</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr"/>
-      <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>类型名称</t>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>school_id</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr"/>
+      <c r="E6" s="16" t="inlineStr">
+        <is>
+          <t>→schools</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="G6" s="13" t="inlineStr"/>
+      <c r="H6" s="13" t="inlineStr">
+        <is>
+          <t>学校ID（外键）</t>
         </is>
       </c>
     </row>
@@ -7342,12 +5886,12 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>code</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>VARCHAR(30)</t>
+          <t>VARCHAR(100)</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr"/>
@@ -7360,7 +5904,7 @@
       <c r="G7" s="4" t="inlineStr"/>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>类型代码（唯一）</t>
+          <t>地点名称</t>
         </is>
       </c>
     </row>
@@ -7375,7 +5919,7 @@
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>VARCHAR(200)</t>
+          <t>VARCHAR(500)</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr"/>
@@ -7398,12 +5942,12 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>sort_order</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>NUMERIC(10,7)</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr"/>
@@ -7413,14 +5957,10 @@
           <t>NOT NULL</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="G9" s="4" t="inlineStr"/>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>排序</t>
+          <t>纬度</t>
         </is>
       </c>
     </row>
@@ -7430,12 +5970,12 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>is_active</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>BOOLEAN</t>
+          <t>NUMERIC(10,7)</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr"/>
@@ -7445,14 +5985,10 @@
           <t>NOT NULL</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
+      <c r="G10" s="4" t="inlineStr"/>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>是否启用</t>
+          <t>经度</t>
         </is>
       </c>
     </row>
@@ -7462,29 +5998,25 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>floor</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>VARCHAR(10)</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr"/>
       <c r="E11" s="4" t="inlineStr"/>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>CURRENT</t>
-        </is>
-      </c>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr"/>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>创建时间</t>
+          <t>楼层</t>
         </is>
       </c>
     </row>
@@ -7494,29 +6026,213 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>building</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>VARCHAR(100)</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr"/>
       <c r="E12" s="4" t="inlineStr"/>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr"/>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>建筑名</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>post_count</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr"/>
+      <c r="E13" s="4" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>关联信息数</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>is_verified</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>BOOLEAN</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr"/>
+      <c r="E14" s="4" t="inlineStr"/>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>是否已验证</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr"/>
+      <c r="E15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>CURRENT</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>创建时间</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr"/>
+      <c r="E16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>CURRENT</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
         <is>
           <t>更新时间</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>is_deleted</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>BOOLEAN</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr"/>
+      <c r="E17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>软删除标记</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>deleted_at</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr"/>
+      <c r="E18" s="4" t="inlineStr"/>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr"/>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>删除时间</t>
         </is>
       </c>
     </row>
@@ -7535,7 +6251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7551,14 +6267,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>tags（标签表）</t>
+          <t>posts（信息表）</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>说明：信息标签，支持官方标签与用户自定义标签</t>
+          <t>说明：核心表，存储校园信息，含6态状态机</t>
         </is>
       </c>
     </row>
@@ -7641,122 +6357,130 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="n">
+      <c r="A6" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>VARCHAR(50)</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr"/>
-      <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>标签名（唯一）</t>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>user_id</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr"/>
+      <c r="E6" s="16" t="inlineStr">
+        <is>
+          <t>→users</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="G6" s="13" t="inlineStr"/>
+      <c r="H6" s="13" t="inlineStr">
+        <is>
+          <t>发布者ID（外键）</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n">
+      <c r="A7" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>slug</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>VARCHAR(60)</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr"/>
-      <c r="E7" s="4" t="inlineStr"/>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr"/>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>标签slug（唯一）</t>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>school_id</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr"/>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>→schools</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="G7" s="13" t="inlineStr"/>
+      <c r="H7" s="13" t="inlineStr">
+        <is>
+          <t>学校ID（外键）</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="n">
+      <c r="A8" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>usage_count</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>INTEGER</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr"/>
-      <c r="E8" s="4" t="inlineStr"/>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>使用次数</t>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>category_id</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr"/>
+      <c r="E8" s="16" t="inlineStr">
+        <is>
+          <t>→categories</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="G8" s="13" t="inlineStr"/>
+      <c r="H8" s="13" t="inlineStr">
+        <is>
+          <t>分类ID（外键）</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n">
+      <c r="A9" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>is_official</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>BOOLEAN</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr"/>
-      <c r="E9" s="4" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>是否官方标签</t>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>location_id</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr"/>
+      <c r="E9" s="16" t="inlineStr">
+        <is>
+          <t>→locations</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="G9" s="13" t="inlineStr"/>
+      <c r="H9" s="13" t="inlineStr">
+        <is>
+          <t>地点ID（外键，可空）</t>
         </is>
       </c>
     </row>
@@ -7766,12 +6490,12 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>title</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>VARCHAR(200)</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr"/>
@@ -7781,14 +6505,10 @@
           <t>NOT NULL</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>CURRENT</t>
-        </is>
-      </c>
+      <c r="G10" s="4" t="inlineStr"/>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>创建时间</t>
+          <t>标题</t>
         </is>
       </c>
     </row>
@@ -7798,12 +6518,12 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>content</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr"/>
@@ -7813,14 +6533,10 @@
           <t>NOT NULL</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>CURRENT</t>
-        </is>
-      </c>
+      <c r="G11" s="4" t="inlineStr"/>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>更新时间</t>
+          <t>内容</t>
         </is>
       </c>
     </row>
@@ -7830,7 +6546,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>is_deleted</t>
+          <t>is_anonymous</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
@@ -7852,7 +6568,7 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>软删除标记</t>
+          <t>是否匿名</t>
         </is>
       </c>
     </row>
@@ -7862,23 +6578,427 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>deleted_at</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr"/>
       <c r="E13" s="4" t="inlineStr"/>
       <c r="F13" s="4" t="inlineStr">
         <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>'pending'</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>状态：6态状态机</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>view_count</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr"/>
+      <c r="E14" s="4" t="inlineStr"/>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>浏览数</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>like_count</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr"/>
+      <c r="E15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>点赞数</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>comment_count</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr"/>
+      <c r="E16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>评论数</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>valid_count</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr"/>
+      <c r="E17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>证实数</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>invalid_count</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr"/>
+      <c r="E18" s="4" t="inlineStr"/>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>证伪数</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>expire_at</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr"/>
+      <c r="E19" s="4" t="inlineStr"/>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr"/>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr"/>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>信息截止时间</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>lost_type</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>VARCHAR(10)</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr"/>
+      <c r="E20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr"/>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>失物类型：lost/found</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>contact_info</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>VARCHAR(255)</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr"/>
+      <c r="E21" s="4" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr"/>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>联系方式</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>is_recommend</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>BOOLEAN</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr"/>
+      <c r="E22" s="4" t="inlineStr"/>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>是否推荐</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr"/>
+      <c r="E23" s="4" t="inlineStr"/>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>CURRENT</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>创建时间</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr"/>
+      <c r="E24" s="4" t="inlineStr"/>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>CURRENT</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>更新时间</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>is_deleted</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>BOOLEAN</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr"/>
+      <c r="E25" s="4" t="inlineStr"/>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>软删除标记</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>deleted_at</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr"/>
+      <c r="E26" s="4" t="inlineStr"/>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr"/>
+      <c r="H26" s="4" t="inlineStr">
         <is>
           <t>删除时间</t>
         </is>
@@ -7899,7 +7019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7915,14 +7035,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>locations（地点表）</t>
+          <t>post_images（信息图片表）</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>说明：校园地点，含经纬度，关联学校</t>
+          <t>说明：信息的附图，一对多关联 Post</t>
         </is>
       </c>
     </row>
@@ -8010,7 +7130,7 @@
       </c>
       <c r="B6" s="14" t="inlineStr">
         <is>
-          <t>school_id</t>
+          <t>post_id</t>
         </is>
       </c>
       <c r="C6" s="15" t="inlineStr">
@@ -8021,7 +7141,7 @@
       <c r="D6" s="13" t="inlineStr"/>
       <c r="E6" s="16" t="inlineStr">
         <is>
-          <t>→schools</t>
+          <t>→posts</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr">
@@ -8032,7 +7152,7 @@
       <c r="G6" s="13" t="inlineStr"/>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>学校ID（外键）</t>
+          <t>信息ID（外键）</t>
         </is>
       </c>
     </row>
@@ -8042,12 +7162,12 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>image_url</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>VARCHAR(100)</t>
+          <t>VARCHAR(500)</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr"/>
@@ -8060,7 +7180,7 @@
       <c r="G7" s="4" t="inlineStr"/>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>地点名称</t>
+          <t>图片URL</t>
         </is>
       </c>
     </row>
@@ -8070,7 +7190,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>thumbnail_url</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -8088,7 +7208,7 @@
       <c r="G8" s="4" t="inlineStr"/>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>描述</t>
+          <t>缩略图URL</t>
         </is>
       </c>
     </row>
@@ -8098,12 +7218,12 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>sort_order</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>NUMERIC(10,7)</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr"/>
@@ -8113,10 +7233,14 @@
           <t>NOT NULL</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr"/>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>纬度</t>
+          <t>排序</t>
         </is>
       </c>
     </row>
@@ -8126,25 +7250,25 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>file_size</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>NUMERIC(10,7)</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr"/>
       <c r="E10" s="4" t="inlineStr"/>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr"/>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>经度</t>
+          <t>文件大小(字节)</t>
         </is>
       </c>
     </row>
@@ -8154,12 +7278,12 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>floor</t>
+          <t>width</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>VARCHAR(10)</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr"/>
@@ -8172,7 +7296,7 @@
       <c r="G11" s="4" t="inlineStr"/>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>楼层</t>
+          <t>宽度(px)</t>
         </is>
       </c>
     </row>
@@ -8182,12 +7306,12 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>height</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>VARCHAR(100)</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr"/>
@@ -8200,7 +7324,7 @@
       <c r="G12" s="4" t="inlineStr"/>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>建筑名</t>
+          <t>高度(px)</t>
         </is>
       </c>
     </row>
@@ -8210,12 +7334,12 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>post_count</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr"/>
@@ -8227,12 +7351,12 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>CURRENT</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>关联信息数</t>
+          <t>创建时间</t>
         </is>
       </c>
     </row>
@@ -8242,7 +7366,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>is_verified</t>
+          <t>is_deleted</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
@@ -8264,7 +7388,7 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>是否已验证</t>
+          <t>软删除标记</t>
         </is>
       </c>
     </row>
@@ -8274,7 +7398,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>deleted_at</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -8286,107 +7410,11 @@
       <c r="E15" s="4" t="inlineStr"/>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>CURRENT</t>
-        </is>
-      </c>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr"/>
       <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>创建时间</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>updated_at</t>
-        </is>
-      </c>
-      <c r="C16" s="12" t="inlineStr">
-        <is>
-          <t>TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr"/>
-      <c r="E16" s="4" t="inlineStr"/>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>CURRENT</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>更新时间</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>is_deleted</t>
-        </is>
-      </c>
-      <c r="C17" s="12" t="inlineStr">
-        <is>
-          <t>BOOLEAN</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr"/>
-      <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>软删除标记</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>deleted_at</t>
-        </is>
-      </c>
-      <c r="C18" s="12" t="inlineStr">
-        <is>
-          <t>TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr"/>
-      <c r="E18" s="4" t="inlineStr"/>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr"/>
-      <c r="H18" s="4" t="inlineStr">
         <is>
           <t>删除时间</t>
         </is>
@@ -8407,7 +7435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -8423,14 +7451,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>posts（信息表）</t>
+          <t>comments（评论表）</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>说明：核心表，存储校园信息，含6态状态机</t>
+          <t>说明：信息评论，支持自引用实现评论回复树</t>
         </is>
       </c>
     </row>
@@ -8518,7 +7546,7 @@
       </c>
       <c r="B6" s="14" t="inlineStr">
         <is>
-          <t>user_id</t>
+          <t>post_id</t>
         </is>
       </c>
       <c r="C6" s="15" t="inlineStr">
@@ -8529,7 +7557,7 @@
       <c r="D6" s="13" t="inlineStr"/>
       <c r="E6" s="16" t="inlineStr">
         <is>
-          <t>→users</t>
+          <t>→posts</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr">
@@ -8540,7 +7568,7 @@
       <c r="G6" s="13" t="inlineStr"/>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>发布者ID（外键）</t>
+          <t>信息ID（外键）</t>
         </is>
       </c>
     </row>
@@ -8550,7 +7578,7 @@
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>school_id</t>
+          <t>user_id</t>
         </is>
       </c>
       <c r="C7" s="15" t="inlineStr">
@@ -8561,7 +7589,7 @@
       <c r="D7" s="13" t="inlineStr"/>
       <c r="E7" s="16" t="inlineStr">
         <is>
-          <t>→schools</t>
+          <t>→users</t>
         </is>
       </c>
       <c r="F7" s="13" t="inlineStr">
@@ -8572,7 +7600,7 @@
       <c r="G7" s="13" t="inlineStr"/>
       <c r="H7" s="13" t="inlineStr">
         <is>
-          <t>学校ID（外键）</t>
+          <t>评论者ID（外键）</t>
         </is>
       </c>
     </row>
@@ -8582,7 +7610,7 @@
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>category_id</t>
+          <t>parent_id</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
@@ -8593,18 +7621,18 @@
       <c r="D8" s="13" t="inlineStr"/>
       <c r="E8" s="16" t="inlineStr">
         <is>
-          <t>→categories</t>
+          <t>→comments</t>
         </is>
       </c>
       <c r="F8" s="13" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="G8" s="13" t="inlineStr"/>
       <c r="H8" s="13" t="inlineStr">
         <is>
-          <t>分类ID（外键）</t>
+          <t>父评论ID（自引用外键）</t>
         </is>
       </c>
     </row>
@@ -8614,7 +7642,7 @@
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>post_type_id</t>
+          <t>reply_to_user_id</t>
         </is>
       </c>
       <c r="C9" s="15" t="inlineStr">
@@ -8625,50 +7653,46 @@
       <c r="D9" s="13" t="inlineStr"/>
       <c r="E9" s="16" t="inlineStr">
         <is>
-          <t>→post_types</t>
+          <t>→users</t>
         </is>
       </c>
       <c r="F9" s="13" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="G9" s="13" t="inlineStr"/>
       <c r="H9" s="13" t="inlineStr">
         <is>
-          <t>类型ID（外键）</t>
+          <t>回复目标用户ID（外键）</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="n">
+      <c r="A10" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>location_id</t>
-        </is>
-      </c>
-      <c r="C10" s="15" t="inlineStr">
-        <is>
-          <t>BIGINT</t>
-        </is>
-      </c>
-      <c r="D10" s="13" t="inlineStr"/>
-      <c r="E10" s="16" t="inlineStr">
-        <is>
-          <t>→locations</t>
-        </is>
-      </c>
-      <c r="F10" s="13" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="G10" s="13" t="inlineStr"/>
-      <c r="H10" s="13" t="inlineStr">
-        <is>
-          <t>地点ID（外键，可空）</t>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>content</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr"/>
+      <c r="E10" s="4" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>评论内容</t>
         </is>
       </c>
     </row>
@@ -8678,12 +7702,12 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>like_count</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>VARCHAR(200)</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr"/>
@@ -8693,10 +7717,14 @@
           <t>NOT NULL</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr"/>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>标题</t>
+          <t>点赞数</t>
         </is>
       </c>
     </row>
@@ -8706,12 +7734,12 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>content</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr"/>
@@ -8721,10 +7749,14 @@
           <t>NOT NULL</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr"/>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>'pending'</t>
+        </is>
+      </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>内容</t>
+          <t>状态</t>
         </is>
       </c>
     </row>
@@ -8734,12 +7766,12 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>is_anonymous</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>BOOLEAN</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr"/>
@@ -8751,12 +7783,12 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>CURRENT</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>是否匿名</t>
+          <t>创建时间</t>
         </is>
       </c>
     </row>
@@ -8766,12 +7798,12 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr"/>
@@ -8783,12 +7815,12 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>'pending'</t>
+          <t>CURRENT</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>状态：6态状态机</t>
+          <t>更新时间</t>
         </is>
       </c>
     </row>
@@ -8798,12 +7830,12 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>view_count</t>
+          <t>is_deleted</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>BOOLEAN</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr"/>
@@ -8815,12 +7847,12 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>浏览数</t>
+          <t>软删除标记</t>
         </is>
       </c>
     </row>
@@ -8830,483 +7862,23 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>like_count</t>
+          <t>deleted_at</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr"/>
       <c r="E16" s="4" t="inlineStr"/>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr"/>
       <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>点赞数</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>comment_count</t>
-        </is>
-      </c>
-      <c r="C17" s="12" t="inlineStr">
-        <is>
-          <t>INTEGER</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr"/>
-      <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>评论数</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>favorite_count</t>
-        </is>
-      </c>
-      <c r="C18" s="12" t="inlineStr">
-        <is>
-          <t>INTEGER</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr"/>
-      <c r="E18" s="4" t="inlineStr"/>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>收藏数</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>valid_count</t>
-        </is>
-      </c>
-      <c r="C19" s="12" t="inlineStr">
-        <is>
-          <t>INTEGER</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr"/>
-      <c r="E19" s="4" t="inlineStr"/>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>证实数</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>invalid_count</t>
-        </is>
-      </c>
-      <c r="C20" s="12" t="inlineStr">
-        <is>
-          <t>INTEGER</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr"/>
-      <c r="E20" s="4" t="inlineStr"/>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>证伪数</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>expire_at</t>
-        </is>
-      </c>
-      <c r="C21" s="12" t="inlineStr">
-        <is>
-          <t>TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr"/>
-      <c r="E21" s="4" t="inlineStr"/>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr"/>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>过期时间</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>activity_start_at</t>
-        </is>
-      </c>
-      <c r="C22" s="12" t="inlineStr">
-        <is>
-          <t>TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr"/>
-      <c r="E22" s="4" t="inlineStr"/>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="inlineStr"/>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>活动开始时间</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>activity_end_at</t>
-        </is>
-      </c>
-      <c r="C23" s="12" t="inlineStr">
-        <is>
-          <t>TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr"/>
-      <c r="E23" s="4" t="inlineStr"/>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr"/>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>活动结束时间</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>lost_type</t>
-        </is>
-      </c>
-      <c r="C24" s="12" t="inlineStr">
-        <is>
-          <t>VARCHAR(10)</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr"/>
-      <c r="E24" s="4" t="inlineStr"/>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="inlineStr"/>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>失物类型：lost/found</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>contact_info</t>
-        </is>
-      </c>
-      <c r="C25" s="12" t="inlineStr">
-        <is>
-          <t>VARCHAR(255)</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr"/>
-      <c r="E25" s="4" t="inlineStr"/>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="inlineStr"/>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>联系方式</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>is_top</t>
-        </is>
-      </c>
-      <c r="C26" s="12" t="inlineStr">
-        <is>
-          <t>BOOLEAN</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr"/>
-      <c r="E26" s="4" t="inlineStr"/>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>是否置顶</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>is_recommend</t>
-        </is>
-      </c>
-      <c r="C27" s="12" t="inlineStr">
-        <is>
-          <t>BOOLEAN</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr"/>
-      <c r="E27" s="4" t="inlineStr"/>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>是否推荐</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>created_at</t>
-        </is>
-      </c>
-      <c r="C28" s="12" t="inlineStr">
-        <is>
-          <t>TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr"/>
-      <c r="E28" s="4" t="inlineStr"/>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G28" s="4" t="inlineStr">
-        <is>
-          <t>CURRENT</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>创建时间</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>updated_at</t>
-        </is>
-      </c>
-      <c r="C29" s="12" t="inlineStr">
-        <is>
-          <t>TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr"/>
-      <c r="E29" s="4" t="inlineStr"/>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G29" s="4" t="inlineStr">
-        <is>
-          <t>CURRENT</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>更新时间</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>is_deleted</t>
-        </is>
-      </c>
-      <c r="C30" s="12" t="inlineStr">
-        <is>
-          <t>BOOLEAN</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr"/>
-      <c r="E30" s="4" t="inlineStr"/>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G30" s="4" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>软删除标记</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>deleted_at</t>
-        </is>
-      </c>
-      <c r="C31" s="12" t="inlineStr">
-        <is>
-          <t>TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr"/>
-      <c r="E31" s="4" t="inlineStr"/>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="G31" s="4" t="inlineStr"/>
-      <c r="H31" s="4" t="inlineStr">
         <is>
           <t>删除时间</t>
         </is>
@@ -9343,14 +7915,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>post_tags（信息标签关联表）</t>
+          <t>likes（点赞表）</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>说明：Post 与 Tag 的多对多关联表</t>
+          <t>说明：用户对信息的点赞记录，post_id+user_id 联合唯一</t>
         </is>
       </c>
     </row>
@@ -9470,7 +8042,7 @@
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>tag_id</t>
+          <t>user_id</t>
         </is>
       </c>
       <c r="C7" s="15" t="inlineStr">
@@ -9481,7 +8053,7 @@
       <c r="D7" s="13" t="inlineStr"/>
       <c r="E7" s="16" t="inlineStr">
         <is>
-          <t>→tags</t>
+          <t>→users</t>
         </is>
       </c>
       <c r="F7" s="13" t="inlineStr">
@@ -9492,7 +8064,7 @@
       <c r="G7" s="13" t="inlineStr"/>
       <c r="H7" s="13" t="inlineStr">
         <is>
-          <t>标签ID（外键）</t>
+          <t>用户ID（外键）</t>
         </is>
       </c>
     </row>
